--- a/education_forms/040_space_debris_awareness_quiz--education_forms.xlsx
+++ b/education_forms/040_space_debris_awareness_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'asteroids'}</t>
+          <t>asteroids</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Asteroids'}</t>
+          <t>Asteroids</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'meteorites'}</t>
+          <t>meteorites</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Meteorites'}</t>
+          <t>Meteorites</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_1957}</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 1957}</t>
+          <t>1957</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_1967}</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 1967}</t>
+          <t>1967</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': '1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'10-100'}</t>
+          <t>10-100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': '10-100'}</t>
+          <t>10-100</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'more_than_100'}</t>
+          <t>more_than_100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'More than 100'}</t>
+          <t>More than 100</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'recycling'}</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Recycling'}</t>
+          <t>Recycling</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'de-orbiting'}</t>
+          <t>de-orbiting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'De-orbiting'}</t>
+          <t>De-orbiting</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Very high'}</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
